--- a/result.xlsx
+++ b/result.xlsx
@@ -507,17 +507,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FRZD</t>
+          <t>JUIB</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>5294</v>
+        <v>9108</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="G3" t="n">
         <v>8399</v>
@@ -592,17 +592,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LOOA</t>
+          <t>ORQB</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="G6" t="n">
         <v>733</v>
@@ -679,17 +679,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PNFI</t>
+          <t>JUIC</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>1190</v>
+        <v>1456</v>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
